--- a/ig/DM-MARS-2026/ValueSet-JDV-J112-SexeAdministratif-ENREG.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J112-SexeAdministratif-ENREG.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20200529120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2020-05-29T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-JDV-J112-SexeAdministratif-ENREG.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J112-SexeAdministratif-ENREG.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20200529120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>retired</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2020-05-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
